--- a/视频排序(4).xlsx
+++ b/视频排序(4).xlsx
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>无奈员工</t>
+          <t>老板又去追热点了</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
